--- a/Vos coordonnées (réponses).xlsx
+++ b/Vos coordonnées (réponses).xlsx
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="222">
   <si>
     <t>Horodateur</t>
   </si>
@@ -716,6 +716,27 @@
   </si>
   <si>
     <t>Éléments de Mécanique (Physique 1)</t>
+  </si>
+  <si>
+    <t>didaouikawthar331@gmail.com</t>
+  </si>
+  <si>
+    <t>didaoui kawthar</t>
+  </si>
+  <si>
+    <t>ديداوي كوثر</t>
+  </si>
+  <si>
+    <t>04 décembre 2003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sidi Bél Abbés </t>
+  </si>
+  <si>
+    <t>Sidi Bél Abbés roché</t>
+  </si>
+  <si>
+    <t>0699099272</t>
   </si>
 </sst>
 </file>
@@ -871,7 +892,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:L26" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:L27" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="12">
     <tableColumn name="Horodateur" id="1"/>
     <tableColumn name="Adresse e-mail" id="2"/>
@@ -2083,6 +2104,44 @@
         <v>31</v>
       </c>
     </row>
+    <row r="27" ht="22.5" customHeight="1">
+      <c r="A27" s="8">
+        <v>46319.78425956018</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>

--- a/Vos coordonnées (réponses).xlsx
+++ b/Vos coordonnées (réponses).xlsx
@@ -46,6 +46,21 @@
         <t xml:space="preserve">Le participant a mis à jour cette valeur.</t>
       </text>
     </comment>
+    <comment authorId="0" ref="K5">
+      <text>
+        <t xml:space="preserve">Le participant a mis à jour cette valeur.</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="L6">
+      <text>
+        <t xml:space="preserve">Le participant a mis à jour cette valeur.</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="L5">
+      <text>
+        <t xml:space="preserve">Le participant a mis à jour cette valeur.</t>
+      </text>
+    </comment>
     <comment authorId="0" ref="L4">
       <text>
         <t xml:space="preserve">Le participant a mis à jour cette valeur.</t>
@@ -71,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="358">
   <si>
     <t>Horodateur</t>
   </si>
@@ -220,57 +235,63 @@
     <t>Algèbre 1</t>
   </si>
   <si>
+    <t>TD, c'est la matière enseignée pour le département ETT seulement</t>
+  </si>
+  <si>
+    <t>Doctorat</t>
+  </si>
+  <si>
+    <t>zoulikhaabed3@gmail.com</t>
+  </si>
+  <si>
+    <t>Abed Zoulikha</t>
+  </si>
+  <si>
+    <t>عابد زوليخة</t>
+  </si>
+  <si>
+    <t>15/01/1980</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sidi bel Abbes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ain el berd .sidi bel Abbes </t>
+  </si>
+  <si>
+    <t>0665697925</t>
+  </si>
+  <si>
+    <t>Énergie et environnement</t>
+  </si>
+  <si>
+    <t>sihemlazergui@gmail.com</t>
+  </si>
+  <si>
+    <t>Lazergui Sihem</t>
+  </si>
+  <si>
+    <t>لزرڨي سهام</t>
+  </si>
+  <si>
+    <t>09/06/2000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sidi Bel Abbes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 rue cheikh el madani - hai el arbi ben mhidi - Gambetta - Sidi Bel Abbes </t>
+  </si>
+  <si>
+    <t>0659768499</t>
+  </si>
+  <si>
+    <t>Analyse 3, Probabilités et statistiques</t>
+  </si>
+  <si>
     <t>TD</t>
   </si>
   <si>
-    <t>zoulikhaabed3@gmail.com</t>
-  </si>
-  <si>
-    <t>Abed Zoulikha</t>
-  </si>
-  <si>
-    <t>عابد زوليخة</t>
-  </si>
-  <si>
-    <t>15/01/1980</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sidi bel Abbes </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ain el berd .sidi bel Abbes </t>
-  </si>
-  <si>
-    <t>0665697925</t>
-  </si>
-  <si>
-    <t>Énergie et environnement</t>
-  </si>
-  <si>
-    <t>sihemlazergui@gmail.com</t>
-  </si>
-  <si>
-    <t>Lazergui Sihem</t>
-  </si>
-  <si>
-    <t>لزرڨي سهام</t>
-  </si>
-  <si>
-    <t>09/06/2000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sidi Bel Abbes </t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 rue cheikh el madani - hai el arbi ben mhidi - Gambetta - Sidi Bel Abbes </t>
-  </si>
-  <si>
-    <t>0659768499</t>
-  </si>
-  <si>
-    <t>Analyse 3, Probabilités et statistiques</t>
-  </si>
-  <si>
     <t>mekhfikhalida87@gmail.com</t>
   </si>
   <si>
@@ -322,9 +343,6 @@
     <t>Commande électrique des mécanismes industriels, Electrotechnique Fondamentale 1, Exploitation des Réseaux électriques, Réseaux de transport et de distribution d'énergie électrique, Réseaux électriques 2, Réseaux électriques industriels, Techniques de protection des réseaux électriques</t>
   </si>
   <si>
-    <t>Doctorat</t>
-  </si>
-  <si>
     <t>djellouli08younes08@gmail.com</t>
   </si>
   <si>
@@ -737,6 +755,412 @@
   </si>
   <si>
     <t>0699099272</t>
+  </si>
+  <si>
+    <t>belkacemkadari@gmail.com</t>
+  </si>
+  <si>
+    <t>Kadari Belkacem</t>
+  </si>
+  <si>
+    <t>قداري بلقاسم</t>
+  </si>
+  <si>
+    <t>12/11/1971</t>
+  </si>
+  <si>
+    <t>Sidi-Bel-Abbès</t>
+  </si>
+  <si>
+    <t>08, Rue Hallouche Chikh , SBA 22000</t>
+  </si>
+  <si>
+    <t>0553282842</t>
+  </si>
+  <si>
+    <t>Electronique Fondamentale 1</t>
+  </si>
+  <si>
+    <t>mouilahka4614@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mouilah Kheira </t>
+  </si>
+  <si>
+    <t>مويلح خيرة</t>
+  </si>
+  <si>
+    <t>30/11/1976</t>
+  </si>
+  <si>
+    <t>Sba</t>
+  </si>
+  <si>
+    <t>0774515828</t>
+  </si>
+  <si>
+    <t>somiadjeziri22@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Djeziri Soumia </t>
+  </si>
+  <si>
+    <t xml:space="preserve">جزيري سمية </t>
+  </si>
+  <si>
+    <t>02/08/1993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cité 210 bâtiment C N°90 sidi Yacine sidi Bel Abbes </t>
+  </si>
+  <si>
+    <t>0540920164</t>
+  </si>
+  <si>
+    <t>wahibaelmestarii@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Mestari Wahiba </t>
+  </si>
+  <si>
+    <t>المستاري وهيبة</t>
+  </si>
+  <si>
+    <t>08/02/1996</t>
+  </si>
+  <si>
+    <t>Wahibaelmestarii@gmail.com</t>
+  </si>
+  <si>
+    <t>127, cité 199 lgts bloc D10. Sidi bel abbes</t>
+  </si>
+  <si>
+    <t>0556130770</t>
+  </si>
+  <si>
+    <t>Etat de l'art du génie électrique, TP electronique fondamentale1/ Tp electrotechnique fondamentale 1</t>
+  </si>
+  <si>
+    <t>abbasmohammed.com@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABBAS Mohammed </t>
+  </si>
+  <si>
+    <t xml:space="preserve">عباس محمد </t>
+  </si>
+  <si>
+    <t>20-04-1997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tlemcen-Tlemcen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mansourah Tlemcen </t>
+  </si>
+  <si>
+    <t>0696562379</t>
+  </si>
+  <si>
+    <t>Machines électriques approfondies, Programmation python, Système de conversion de l'énergie éolienne</t>
+  </si>
+  <si>
+    <t>laidabdelali@gmail.com</t>
+  </si>
+  <si>
+    <t>Abdelali laid</t>
+  </si>
+  <si>
+    <t>عبد العالي العيد</t>
+  </si>
+  <si>
+    <t>30/10/1981</t>
+  </si>
+  <si>
+    <t>sidi lahcen</t>
+  </si>
+  <si>
+    <t>cites 800 AADL route de tessala sidi bel abbes</t>
+  </si>
+  <si>
+    <t>0657662517</t>
+  </si>
+  <si>
+    <t>Electronique Fondamentale 1, Electrotechnique Fondamentale 1</t>
+  </si>
+  <si>
+    <t>abdelli.mama@gmail.com</t>
+  </si>
+  <si>
+    <t>Abdelli mama</t>
+  </si>
+  <si>
+    <t>عبدلي مامة</t>
+  </si>
+  <si>
+    <t>25/02/1978</t>
+  </si>
+  <si>
+    <t>Tanira</t>
+  </si>
+  <si>
+    <t>Abdelli.mama@gmail.com</t>
+  </si>
+  <si>
+    <t>0552968922</t>
+  </si>
+  <si>
+    <t>Algèbre 1, Analyse 1</t>
+  </si>
+  <si>
+    <t>sacihamza40@gmail.com</t>
+  </si>
+  <si>
+    <t>saci hamza</t>
+  </si>
+  <si>
+    <t>ساسي حمزة</t>
+  </si>
+  <si>
+    <t>20/05/1991</t>
+  </si>
+  <si>
+    <t>khenchela</t>
+  </si>
+  <si>
+    <t>Rue d'hôpital Khenchela</t>
+  </si>
+  <si>
+    <t>0540025158</t>
+  </si>
+  <si>
+    <t>Éléments de Mécanique (Physique 1), Énergie et environnement</t>
+  </si>
+  <si>
+    <t>attarimad3@gmail.com</t>
+  </si>
+  <si>
+    <t>Attar Imad</t>
+  </si>
+  <si>
+    <t>عطار عماد</t>
+  </si>
+  <si>
+    <t>13/08/1991</t>
+  </si>
+  <si>
+    <t>Sfisef</t>
+  </si>
+  <si>
+    <t>Elmakam sidi bel abbes</t>
+  </si>
+  <si>
+    <t>0656697602</t>
+  </si>
+  <si>
+    <t>Algèbre 1, Analyse 3</t>
+  </si>
+  <si>
+    <t>bensenadanadia3@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bensenada Nadia aouicha </t>
+  </si>
+  <si>
+    <t>بن سنادة نادية عويشة</t>
+  </si>
+  <si>
+    <t>02-07-1994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilaya de sidi Bel Abbes </t>
+  </si>
+  <si>
+    <t>Numéro 146 lot n"01sidi Djilali sba</t>
+  </si>
+  <si>
+    <t>0652183005</t>
+  </si>
+  <si>
+    <t>Histoire de L’Algérie</t>
+  </si>
+  <si>
+    <t>hadilyamoune@gmail.com</t>
+  </si>
+  <si>
+    <t>Yamoune fatima zohra hadil</t>
+  </si>
+  <si>
+    <t>يامون فاطمة الزهراء هديل</t>
+  </si>
+  <si>
+    <t>29/09/2003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N=9 rue de setif sidi bel abbes </t>
+  </si>
+  <si>
+    <t>0697176260</t>
+  </si>
+  <si>
+    <t>Probabilités et statistiques</t>
+  </si>
+  <si>
+    <t>inesfilali2003@gmail.com</t>
+  </si>
+  <si>
+    <t>Filali Ines nafissa</t>
+  </si>
+  <si>
+    <t>فيلالي ايناس نفيسة</t>
+  </si>
+  <si>
+    <t>30/12/2003</t>
+  </si>
+  <si>
+    <t>0791848652</t>
+  </si>
+  <si>
+    <t>Electricité fondamentale</t>
+  </si>
+  <si>
+    <t>khalifamir95maths@gmail.com</t>
+  </si>
+  <si>
+    <t>Mir Khelifa</t>
+  </si>
+  <si>
+    <t>مير خليفة</t>
+  </si>
+  <si>
+    <t>10-04-1995</t>
+  </si>
+  <si>
+    <t>belarbi Sidi Bel Abbès</t>
+  </si>
+  <si>
+    <t>khelifa-mir@outlook.fr</t>
+  </si>
+  <si>
+    <t>Belarbi</t>
+  </si>
+  <si>
+    <t>0550634948</t>
+  </si>
+  <si>
+    <t>Analyse 3</t>
+  </si>
+  <si>
+    <t>wassila.drouni@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drouni Wassila Abir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">دروني وسيلة عبير </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/12/1995 </t>
+  </si>
+  <si>
+    <t>Wassila.drouni@gmail.com</t>
+  </si>
+  <si>
+    <t>Éléments de Mécanique (Physique 1), Ethique, déontologie et propriété intellectuelle, Ondes et vibrations</t>
+  </si>
+  <si>
+    <t>mahkouka.zaza@gmail.com</t>
+  </si>
+  <si>
+    <t>Mahkouka zaza</t>
+  </si>
+  <si>
+    <t>محكوكة زازة</t>
+  </si>
+  <si>
+    <t>22-11-2001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hay el badr sidi bel abbes
+</t>
+  </si>
+  <si>
+    <t>0778360776</t>
+  </si>
+  <si>
+    <t>Electrotechnique fondamentale, Production de l'énergie électrique, μ-processeurs et μ-contrôleurs</t>
+  </si>
+  <si>
+    <t>mehadjiameslem@gmail.com</t>
+  </si>
+  <si>
+    <t>MESLEM Mehadjia</t>
+  </si>
+  <si>
+    <t>مسلم مهاجية</t>
+  </si>
+  <si>
+    <t>02/03/1994</t>
+  </si>
+  <si>
+    <t>M'cid</t>
+  </si>
+  <si>
+    <t>0697013439</t>
+  </si>
+  <si>
+    <t>Electrotechnique Fondamentale 1, Programmation python</t>
+  </si>
+  <si>
+    <t>belaidiouafia77@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belaidi Ouafia </t>
+  </si>
+  <si>
+    <t>بلعيدي وافية</t>
+  </si>
+  <si>
+    <t>22/05/1991</t>
+  </si>
+  <si>
+    <t>Frenda Tiaret</t>
+  </si>
+  <si>
+    <t>belaidi.ouafia@outlook.fr</t>
+  </si>
+  <si>
+    <t>cité Moulay  Abdel-Kader 50 logement N° 22</t>
+  </si>
+  <si>
+    <t>0668834015</t>
+  </si>
+  <si>
+    <t>Electronique appliquée</t>
+  </si>
+  <si>
+    <t>megdz100@gmail.com</t>
+  </si>
+  <si>
+    <t>MEGUEDAD ABOUBAKR</t>
+  </si>
+  <si>
+    <t>مقداد أبوبكر</t>
+  </si>
+  <si>
+    <t>20/07/1994</t>
+  </si>
+  <si>
+    <t>ZAHANA/MASCARA</t>
+  </si>
+  <si>
+    <t>CITE MOUDJAHIDINE</t>
+  </si>
+  <si>
+    <t>0799491736</t>
+  </si>
+  <si>
+    <t>Commande des machines électriques, Commande électrique</t>
   </si>
 </sst>
 </file>
@@ -892,7 +1316,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:L27" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:L45" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="12">
     <tableColumn name="Horodateur" id="1"/>
     <tableColumn name="Adresse e-mail" id="2"/>
@@ -1238,7 +1662,7 @@
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="8">
-        <v>46318.64698238426</v>
+        <v>46321.28902592593</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>32</v>
@@ -1276,7 +1700,7 @@
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="8">
-        <v>46318.54014431713</v>
+        <v>46320.94516415509</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>40</v>
@@ -1308,77 +1732,81 @@
       <c r="K5" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="L5" s="12"/>
+      <c r="L5" s="9" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="8">
-        <v>46318.54120715278</v>
+        <v>46319.99802958334</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C6" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>50</v>
-      </c>
       <c r="H6" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="L6" s="12"/>
+      <c r="L6" s="9" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="8">
         <v>46318.54991810185</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C7" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>58</v>
-      </c>
       <c r="H7" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="L7" s="12"/>
     </row>
@@ -1387,34 +1815,34 @@
         <v>46318.68299155093</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D8" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G8" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>66</v>
-      </c>
       <c r="H8" s="9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L8" s="9" t="s">
         <v>20</v>
@@ -1425,37 +1853,37 @@
         <v>46318.77010581018</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C9" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="K9" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>74</v>
-      </c>
       <c r="L9" s="9" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
@@ -1463,37 +1891,37 @@
         <v>46318.64713875</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C10" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="G10" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="D10" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>84</v>
-      </c>
       <c r="H10" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
@@ -1501,37 +1929,37 @@
         <v>46318.65132887731</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C11" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="D11" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>92</v>
-      </c>
       <c r="H11" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
@@ -1539,37 +1967,37 @@
         <v>46318.76164221065</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C12" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="G12" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="D12" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>100</v>
-      </c>
       <c r="H12" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
@@ -1577,37 +2005,37 @@
         <v>46318.708214618055</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
@@ -1615,34 +2043,34 @@
         <v>46318.73081009259</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C14" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G14" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="D14" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>117</v>
-      </c>
       <c r="H14" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>48</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="L14" s="9" t="s">
         <v>31</v>
@@ -1653,37 +2081,37 @@
         <v>46318.73850689815</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K15" s="9" t="s">
         <v>19</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
@@ -1691,28 +2119,28 @@
         <v>46318.77560972222</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C16" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G16" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="D16" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>132</v>
-      </c>
       <c r="H16" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J16" s="9" t="s">
         <v>29</v>
@@ -1729,31 +2157,31 @@
         <v>46318.82518136574</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C17" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="G17" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="D17" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>138</v>
-      </c>
       <c r="H17" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K17" s="9" t="s">
         <v>30</v>
@@ -1767,34 +2195,34 @@
         <v>46318.83632082176</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C18" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="G18" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D18" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>146</v>
-      </c>
       <c r="H18" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K18" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L18" s="9" t="s">
         <v>31</v>
@@ -1805,34 +2233,34 @@
         <v>46318.88105693287</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C19" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G19" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="D19" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>154</v>
-      </c>
       <c r="H19" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L19" s="9" t="s">
         <v>20</v>
@@ -1843,37 +2271,37 @@
         <v>46318.92513883102</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C20" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="G20" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="D20" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>161</v>
-      </c>
       <c r="H20" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
@@ -1881,37 +2309,37 @@
         <v>46319.35340493056</v>
       </c>
       <c r="B21" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="J21" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="C21" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>168</v>
-      </c>
       <c r="K21" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
@@ -1919,37 +2347,37 @@
         <v>46319.50771797454</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C22" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="G22" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="D22" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>177</v>
-      </c>
       <c r="H22" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" ht="22.5" customHeight="1">
@@ -1957,37 +2385,37 @@
         <v>46319.521528067125</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C23" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="G23" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="D23" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>185</v>
-      </c>
       <c r="H23" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K23" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L23" s="9" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
@@ -1995,37 +2423,37 @@
         <v>46319.61433247685</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C24" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="G24" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="D24" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>193</v>
-      </c>
       <c r="H24" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L24" s="9" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" ht="22.5" customHeight="1">
@@ -2033,31 +2461,31 @@
         <v>46319.64934394676</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C25" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="G25" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="D25" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>200</v>
-      </c>
       <c r="H25" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K25" s="9" t="s">
         <v>30</v>
@@ -2071,34 +2499,34 @@
         <v>46319.74269109954</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C26" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="G26" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="D26" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>207</v>
-      </c>
       <c r="H26" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K26" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L26" s="9" t="s">
         <v>31</v>
@@ -2109,37 +2537,721 @@
         <v>46319.78425956018</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C27" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="G27" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="D27" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>215</v>
-      </c>
       <c r="H27" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K27" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L27" s="9" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="28" ht="22.5" customHeight="1">
+      <c r="A28" s="8">
+        <v>46320.01936986111</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" ht="22.5" customHeight="1">
+      <c r="A29" s="8">
+        <v>46321.280724282406</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" ht="22.5" customHeight="1">
+      <c r="A30" s="8">
+        <v>46321.28163103009</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" ht="22.5" customHeight="1">
+      <c r="A31" s="8">
+        <v>46321.29162662037</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" ht="22.5" customHeight="1">
+      <c r="A32" s="8">
+        <v>46321.29205873843</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="K32" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="L32" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" ht="22.5" customHeight="1">
+      <c r="A33" s="8">
+        <v>46321.29804105324</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" ht="22.5" customHeight="1">
+      <c r="A34" s="8">
+        <v>46321.30419847222</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" ht="22.5" customHeight="1">
+      <c r="A35" s="8">
+        <v>46321.31509979167</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="I35" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="L35" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" ht="22.5" customHeight="1">
+      <c r="A36" s="8">
+        <v>46321.31591075231</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="L36" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" ht="22.5" customHeight="1">
+      <c r="A37" s="8">
+        <v>46321.32197607639</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="J37" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="K37" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="L37" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" ht="22.5" customHeight="1">
+      <c r="A38" s="8">
+        <v>46321.336943159724</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="J38" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="K38" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="L38" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" ht="22.5" customHeight="1">
+      <c r="A39" s="8">
+        <v>46321.349378750005</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="J39" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="K39" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="L39" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" ht="22.5" customHeight="1">
+      <c r="A40" s="8">
+        <v>46321.370668958334</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="I40" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="K40" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="L40" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" ht="22.5" customHeight="1">
+      <c r="A41" s="8">
+        <v>46321.39756121528</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I41" s="9">
+        <v>5.61243819E8</v>
+      </c>
+      <c r="J41" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="K41" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="L41" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" ht="22.5" customHeight="1">
+      <c r="A42" s="8">
+        <v>46321.43377498843</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="I42" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="J42" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="K42" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="L42" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" ht="22.5" customHeight="1">
+      <c r="A43" s="8">
+        <v>46321.44254275463</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="I43" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="J43" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="K43" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="L43" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" ht="22.5" customHeight="1">
+      <c r="A44" s="8">
+        <v>46321.73322538195</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="I44" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="J44" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="K44" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="L44" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" ht="22.5" customHeight="1">
+      <c r="A45" s="8">
+        <v>46321.75854954861</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="I45" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="K45" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="L45" s="9" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
